--- a/data/trans_orig/IP06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP06-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34312</t>
+          <t>34985</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>30515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46112</t>
+          <t>46144</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29484</t>
+          <t>30085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45172</t>
+          <t>45768</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64765</t>
+          <t>65174</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86457</t>
+          <t>88106</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45204</t>
+          <t>45612</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61266</t>
+          <t>62194</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58632</t>
+          <t>58500</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76107</t>
+          <t>75454</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108509</t>
+          <t>108557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132369</t>
+          <t>132864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18731</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34050</t>
+          <t>34788</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29096</t>
+          <t>29183</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37139</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>58847</t>
+          <t>56708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7436</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57863</t>
+          <t>58364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80822</t>
+          <t>81528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58497</t>
+          <t>57236</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80973</t>
+          <t>80488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123062</t>
+          <t>123273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154929</t>
+          <t>154916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>144382</t>
+          <t>144796</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>169616</t>
+          <t>169532</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>147835</t>
+          <t>148674</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>171672</t>
+          <t>172466</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>299763</t>
+          <t>299800</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>333863</t>
+          <t>334273</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,02%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12546</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25498</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18258</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39510</t>
+          <t>39052</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27366</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43874</t>
+          <t>43185</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29438</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46794</t>
+          <t>46110</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61710</t>
+          <t>61346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84716</t>
+          <t>86344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64500</t>
+          <t>63747</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81686</t>
+          <t>81323</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79242</t>
+          <t>80021</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97935</t>
+          <t>97809</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>149873</t>
+          <t>149171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174829</t>
+          <t>175804</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28455</t>
+          <t>29355</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>26531</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30851</t>
+          <t>32067</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50417</t>
+          <t>51033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15710</t>
+          <t>16172</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42399</t>
+          <t>42855</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61985</t>
+          <t>63031</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49933</t>
+          <t>51066</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72779</t>
+          <t>71803</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99814</t>
+          <t>99077</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>130215</t>
+          <t>128427</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105460</t>
+          <t>104819</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127215</t>
+          <t>126048</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107565</t>
+          <t>107572</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131447</t>
+          <t>130859</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>218216</t>
+          <t>220014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>250835</t>
+          <t>251747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,02%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65212</t>
+          <t>64989</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>92110</t>
+          <t>91919</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54020</t>
+          <t>54844</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78123</t>
+          <t>80245</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>126939</t>
+          <t>127448</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>162040</t>
+          <t>163766</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>23318</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32073</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>174733</t>
+          <t>175235</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>212872</t>
+          <t>214808</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>185003</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>222777</t>
+          <t>223767</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>373172</t>
+          <t>372173</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>424209</t>
+          <t>426882</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>378413</t>
+          <t>376609</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>419881</t>
+          <t>419789</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>415162</t>
+          <t>414848</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>457041</t>
+          <t>456953</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>807728</t>
+          <t>804653</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>864873</t>
+          <t>865819</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,8%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>19204</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16039</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31208</t>
+          <t>32007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33145</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50846</t>
+          <t>51263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41209</t>
+          <t>41265</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60938</t>
+          <t>60254</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80257</t>
+          <t>79625</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104954</t>
+          <t>106230</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83266</t>
+          <t>83258</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102080</t>
+          <t>101476</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69877</t>
+          <t>69464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90445</t>
+          <t>88937</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>158481</t>
+          <t>158006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>185433</t>
+          <t>186740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22682</t>
+          <t>21672</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16872</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33786</t>
+          <t>33020</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30105</t>
+          <t>29833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51016</t>
+          <t>50850</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52225</t>
+          <t>52540</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74132</t>
+          <t>73935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73542</t>
+          <t>73494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99688</t>
+          <t>98111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130288</t>
+          <t>130747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>165222</t>
+          <t>164819</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143800</t>
+          <t>143526</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>167319</t>
+          <t>166069</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>142325</t>
+          <t>143519</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>170112</t>
+          <t>169694</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>294347</t>
+          <t>293949</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>330633</t>
+          <t>331234</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19975</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37201</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11179</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38434</t>
+          <t>37909</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57333</t>
+          <t>57831</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42563</t>
+          <t>42388</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61165</t>
+          <t>62078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86291</t>
+          <t>86062</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113699</t>
+          <t>113527</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79941</t>
+          <t>80295</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101069</t>
+          <t>101252</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81418</t>
+          <t>81397</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101507</t>
+          <t>101139</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165813</t>
+          <t>169073</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194959</t>
+          <t>196974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,41%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20858</t>
+          <t>20437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20286</t>
+          <t>19348</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19663</t>
+          <t>19795</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37680</t>
+          <t>37826</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37952</t>
+          <t>39436</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57774</t>
+          <t>59154</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41965</t>
+          <t>42934</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>63683</t>
+          <t>62377</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>86731</t>
+          <t>87544</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>113839</t>
+          <t>114724</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94087</t>
+          <t>93556</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>114844</t>
+          <t>115249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>94343</t>
+          <t>94290</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116628</t>
+          <t>116061</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196422</t>
+          <t>195218</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>226450</t>
+          <t>225365</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,43%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44177</t>
+          <t>44080</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67485</t>
+          <t>68015</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51021</t>
+          <t>51175</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78783</t>
+          <t>77619</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>99098</t>
+          <t>101921</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134250</t>
+          <t>137613</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20589</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37227</t>
+          <t>37372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>178892</t>
+          <t>179692</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>218806</t>
+          <t>218660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>219488</t>
+          <t>220119</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>262649</t>
+          <t>263456</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>411370</t>
+          <t>412275</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>467524</t>
+          <t>470297</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>423095</t>
+          <t>422645</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>465248</t>
+          <t>464125</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>409879</t>
+          <t>410542</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>454816</t>
+          <t>455587</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>846905</t>
+          <t>846657</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>908413</t>
+          <t>909090</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -6886,12 +6886,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14669</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>17512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27829</t>
+          <t>28433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>23265</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39335</t>
+          <t>38212</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20226</t>
+          <t>20440</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34985</t>
+          <t>35602</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47774</t>
+          <t>46954</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68384</t>
+          <t>68663</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82403</t>
+          <t>82547</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99103</t>
+          <t>98627</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75160</t>
+          <t>75229</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91570</t>
+          <t>91927</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163717</t>
+          <t>162217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>187320</t>
+          <t>186629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31610</t>
+          <t>31724</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29272</t>
+          <t>29444</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48716</t>
+          <t>48593</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7568,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12659</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7681,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48500</t>
+          <t>48369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68052</t>
+          <t>67087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51195</t>
+          <t>51175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72823</t>
+          <t>72081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103889</t>
+          <t>103712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>134048</t>
+          <t>133586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123412</t>
+          <t>122822</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143630</t>
+          <t>143955</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157985</t>
+          <t>157930</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181955</t>
+          <t>181982</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>287994</t>
+          <t>287678</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>319768</t>
+          <t>321243</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27998</t>
+          <t>28491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22962</t>
+          <t>23050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26658</t>
+          <t>27355</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45748</t>
+          <t>46595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>19513</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29774</t>
+          <t>28863</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47734</t>
+          <t>47500</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34283</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54198</t>
+          <t>53556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69637</t>
+          <t>69842</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96168</t>
+          <t>95620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110422</t>
+          <t>108892</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131849</t>
+          <t>131522</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>113949</t>
+          <t>112728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135497</t>
+          <t>135845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>231132</t>
+          <t>230237</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>262096</t>
+          <t>262151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17511</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18732</t>
+          <t>19138</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32680</t>
+          <t>32629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>747</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12606</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>28888</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46396</t>
+          <t>45647</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43738</t>
+          <t>44038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59357</t>
+          <t>59678</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>84253</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110125</t>
+          <t>111685</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130255</t>
+          <t>130434</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113966</t>
+          <t>114668</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>135200</t>
+          <t>134041</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230379</t>
+          <t>230935</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>259258</t>
+          <t>258389</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44459</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67429</t>
+          <t>69407</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49890</t>
+          <t>50467</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75597</t>
+          <t>76897</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>100410</t>
+          <t>102634</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134263</t>
+          <t>135872</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143340</t>
+          <t>145741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>181036</t>
+          <t>181763</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149857</t>
+          <t>149442</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>187645</t>
+          <t>185994</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>304455</t>
+          <t>304775</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>357538</t>
+          <t>356708</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>447027</t>
+          <t>444353</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>487702</t>
+          <t>485727</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>479772</t>
+          <t>483533</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>524566</t>
+          <t>524644</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>939566</t>
+          <t>940932</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>998594</t>
+          <t>999045</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
